--- a/phase2_Advanced_Excel_Pandas/Day23_Power_Query_ETL/day23_raw_sales.xlsx
+++ b/phase2_Advanced_Excel_Pandas/Day23_Power_Query_ETL/day23_raw_sales.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c5ea84ffcf41a175/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{CF6527F5-7FCC-43D9-AC98-40049AFC4CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B910C53F-290F-4243-A4E4-1160D46E2167}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{CF6527F5-7FCC-43D9-AC98-40049AFC4CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6153ECDD-2126-458E-BE83-719D3D232976}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF55EAC7-F197-4636-B1D0-529AA05E410C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AF55EAC7-F197-4636-B1D0-529AA05E410C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Table1" sheetId="3" r:id="rId1"/>
-    <sheet name="raw_data" sheetId="1" r:id="rId2"/>
+    <sheet name="raw_data" sheetId="1" r:id="rId1"/>
+    <sheet name="final_sheet" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Table1!$A$1:$F$8</definedName>
+    <definedName name="ExternalData_1" localSheetId="1" hidden="1">final_sheet!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -164,15 +164,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -181,9 +183,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
@@ -201,6 +200,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{0FF8A921-A5F3-4CD4-B5BF-E7F230EA7075}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="7">
@@ -217,32 +220,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3586A940-E4EC-4B0D-8852-1F67B276AC78}" name="Table1_1" displayName="Table1_1" ref="A1:F8" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F8" xr:uid="{3586A940-E4EC-4B0D-8852-1F67B276AC78}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8F6C90D5-427B-4B54-99A8-F8BAA3595F63}" uniqueName="1" name="Order ID" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{58FE73B3-4C1F-4D25-96D6-7CC6F1CE7C7B}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{7C6D61BF-B137-4B34-9104-67B2EB9BE19A}" uniqueName="3" name="Sales Rep" queryTableFieldId="3" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{E4ED8053-E7D6-4ED8-A27C-1A6562FA58D2}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{2288D27F-10E5-474C-873C-E2BD685E6C6B}" uniqueName="5" name="Amount" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{4DA42F53-4DA7-48BD-B7A5-BB89E6446ED6}" uniqueName="6" name="Status" queryTableFieldId="6" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73D4B68D-C35E-4659-B5E8-19056F1DB814}" name="Table1" displayName="Table1" ref="A1:F9" totalsRowShown="0">
   <autoFilter ref="A1:F9" xr:uid="{73D4B68D-C35E-4659-B5E8-19056F1DB814}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{5564D1BD-2B22-4902-9CEA-6AA826E81D2E}" name="Order ID"/>
-    <tableColumn id="2" xr3:uid="{649CAC8F-EA6B-4CB5-BA4C-2D07D169E0D3}" name="Date" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{649CAC8F-EA6B-4CB5-BA4C-2D07D169E0D3}" name="Date" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{7FB290EC-C19D-4F6C-B4D0-F328D8E1B771}" name="Sales Rep"/>
     <tableColumn id="4" xr3:uid="{51312D99-40DF-45F1-9341-07405A4C0A7E}" name="Region"/>
     <tableColumn id="5" xr3:uid="{A0073875-B368-41C2-9384-65047816FDD8}" name="Amount"/>
     <tableColumn id="6" xr3:uid="{5AB0CFD7-55C0-47BB-86F8-F10D33221C0B}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3586A940-E4EC-4B0D-8852-1F67B276AC78}" name="Table1_1" displayName="Table1_1" ref="A1:F8" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:F8" xr:uid="{3586A940-E4EC-4B0D-8852-1F67B276AC78}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{8F6C90D5-427B-4B54-99A8-F8BAA3595F63}" uniqueName="1" name="Order ID" queryTableFieldId="1"/>
+    <tableColumn id="2" xr3:uid="{58FE73B3-4C1F-4D25-96D6-7CC6F1CE7C7B}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{7C6D61BF-B137-4B34-9104-67B2EB9BE19A}" uniqueName="3" name="Sales Rep" queryTableFieldId="3" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{E4ED8053-E7D6-4ED8-A27C-1A6562FA58D2}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{2288D27F-10E5-474C-873C-E2BD685E6C6B}" uniqueName="5" name="Amount" queryTableFieldId="5"/>
+    <tableColumn id="6" xr3:uid="{4DA42F53-4DA7-48BD-B7A5-BB89E6446ED6}" uniqueName="6" name="Status" queryTableFieldId="6" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -562,6 +565,199 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{843E34D1-E7B6-4A3B-9A1E-D8C6B6CD195C}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2" s="1">
+        <v>45296</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>45000</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>102</v>
+      </c>
+      <c r="B3" s="1">
+        <v>45297</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3">
+        <v>32000</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>103</v>
+      </c>
+      <c r="B4" s="1">
+        <v>45298</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>104</v>
+      </c>
+      <c r="B5" s="1">
+        <v>45299</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>78000</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>105</v>
+      </c>
+      <c r="B6" s="1">
+        <v>45300</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>52000</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>106</v>
+      </c>
+      <c r="B7" s="1">
+        <v>45301</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>29000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>107</v>
+      </c>
+      <c r="B8" s="1">
+        <v>45302</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>61000</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>108</v>
+      </c>
+      <c r="B9" s="1">
+        <v>45303</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>15000</v>
+      </c>
+      <c r="F9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E45A5CE-FB4C-49AC-B761-6CEC1EB5CA58}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -601,16 +797,16 @@
       <c r="B2" s="1">
         <v>45296</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
       <c r="E2">
         <v>45000</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -621,16 +817,16 @@
       <c r="B3" s="1">
         <v>45297</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>20</v>
       </c>
       <c r="E3">
         <v>32000</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -641,16 +837,16 @@
       <c r="B4" s="1">
         <v>45298</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -661,16 +857,16 @@
       <c r="B5" s="1">
         <v>45299</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5">
         <v>78000</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -681,16 +877,16 @@
       <c r="B6" s="1">
         <v>45300</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>20</v>
       </c>
       <c r="E6">
         <v>52000</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>8</v>
       </c>
     </row>
@@ -701,16 +897,16 @@
       <c r="B7" s="1">
         <v>45302</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>18</v>
       </c>
       <c r="E7">
         <v>61000</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -721,209 +917,16 @@
       <c r="B8" s="1">
         <v>45303</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8">
         <v>15000</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{843E34D1-E7B6-4A3B-9A1E-D8C6B6CD195C}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>101</v>
-      </c>
-      <c r="B2" s="1">
-        <v>45296</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2">
-        <v>45000</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>102</v>
-      </c>
-      <c r="B3" s="1">
-        <v>45297</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3">
-        <v>32000</v>
-      </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>103</v>
-      </c>
-      <c r="B4" s="1">
-        <v>45298</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>104</v>
-      </c>
-      <c r="B5" s="1">
-        <v>45299</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5">
-        <v>78000</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>105</v>
-      </c>
-      <c r="B6" s="1">
-        <v>45300</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>52000</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>106</v>
-      </c>
-      <c r="B7" s="1">
-        <v>45301</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7">
-        <v>29000</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>107</v>
-      </c>
-      <c r="B8" s="1">
-        <v>45302</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>61000</v>
-      </c>
       <c r="F8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>108</v>
-      </c>
-      <c r="B9" s="1">
-        <v>45303</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9">
-        <v>15000</v>
-      </c>
-      <c r="F9" t="s">
         <v>6</v>
       </c>
     </row>
